--- a/artfynd/A 18270-2024 artfynd.xlsx
+++ b/artfynd/A 18270-2024 artfynd.xlsx
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119796559</v>
+        <v>119796562</v>
       </c>
       <c r="B7" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416231</v>
+        <v>416224</v>
       </c>
       <c r="R7" t="n">
-        <v>6814920</v>
+        <v>6814940</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119796562</v>
+        <v>119796559</v>
       </c>
       <c r="B8" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416224</v>
+        <v>416231</v>
       </c>
       <c r="R8" t="n">
-        <v>6814940</v>
+        <v>6814920</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 18270-2024 artfynd.xlsx
+++ b/artfynd/A 18270-2024 artfynd.xlsx
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119796562</v>
+        <v>119796559</v>
       </c>
       <c r="B7" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416224</v>
+        <v>416231</v>
       </c>
       <c r="R7" t="n">
-        <v>6814940</v>
+        <v>6814920</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119796559</v>
+        <v>119796562</v>
       </c>
       <c r="B8" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416231</v>
+        <v>416224</v>
       </c>
       <c r="R8" t="n">
-        <v>6814920</v>
+        <v>6814940</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119796376</v>
+        <v>119796558</v>
       </c>
       <c r="B9" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416228</v>
+        <v>416230</v>
       </c>
       <c r="R9" t="n">
         <v>6814930</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119796558</v>
+        <v>119796376</v>
       </c>
       <c r="B10" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416230</v>
+        <v>416228</v>
       </c>
       <c r="R10" t="n">
         <v>6814930</v>

--- a/artfynd/A 18270-2024 artfynd.xlsx
+++ b/artfynd/A 18270-2024 artfynd.xlsx
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119796562</v>
+        <v>119796558</v>
       </c>
       <c r="B8" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416224</v>
+        <v>416230</v>
       </c>
       <c r="R8" t="n">
-        <v>6814940</v>
+        <v>6814930</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119796558</v>
+        <v>119796562</v>
       </c>
       <c r="B9" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416230</v>
+        <v>416224</v>
       </c>
       <c r="R9" t="n">
-        <v>6814930</v>
+        <v>6814940</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 18270-2024 artfynd.xlsx
+++ b/artfynd/A 18270-2024 artfynd.xlsx
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119796559</v>
+        <v>119796562</v>
       </c>
       <c r="B7" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416231</v>
+        <v>416224</v>
       </c>
       <c r="R7" t="n">
-        <v>6814920</v>
+        <v>6814940</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119796558</v>
+        <v>119796559</v>
       </c>
       <c r="B8" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416230</v>
+        <v>416231</v>
       </c>
       <c r="R8" t="n">
-        <v>6814930</v>
+        <v>6814920</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119796562</v>
+        <v>119796558</v>
       </c>
       <c r="B9" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416224</v>
+        <v>416230</v>
       </c>
       <c r="R9" t="n">
-        <v>6814940</v>
+        <v>6814930</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 18270-2024 artfynd.xlsx
+++ b/artfynd/A 18270-2024 artfynd.xlsx
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119796562</v>
+        <v>119796558</v>
       </c>
       <c r="B7" t="n">
-        <v>78262</v>
+        <v>79160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416224</v>
+        <v>416230</v>
       </c>
       <c r="R7" t="n">
-        <v>6814940</v>
+        <v>6814930</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
         <v>119796559</v>
       </c>
       <c r="B8" t="n">
-        <v>78263</v>
+        <v>78279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119796558</v>
+        <v>119796376</v>
       </c>
       <c r="B9" t="n">
-        <v>79144</v>
+        <v>78187</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>416230</v>
+        <v>416228</v>
       </c>
       <c r="R9" t="n">
         <v>6814930</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119796376</v>
+        <v>119796562</v>
       </c>
       <c r="B10" t="n">
-        <v>78171</v>
+        <v>78278</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>416228</v>
+        <v>416224</v>
       </c>
       <c r="R10" t="n">
-        <v>6814930</v>
+        <v>6814940</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 18270-2024 artfynd.xlsx
+++ b/artfynd/A 18270-2024 artfynd.xlsx
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119796558</v>
+        <v>119796559</v>
       </c>
       <c r="B7" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>416230</v>
+        <v>416231</v>
       </c>
       <c r="R7" t="n">
-        <v>6814930</v>
+        <v>6814920</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119796559</v>
+        <v>119796558</v>
       </c>
       <c r="B8" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>416231</v>
+        <v>416230</v>
       </c>
       <c r="R8" t="n">
-        <v>6814920</v>
+        <v>6814930</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
